--- a/feature/51-supprimer-les-exemples-de-longlet-ressources-par-cas-dusage/ig/StructureDefinition-FrPractitionerAgregateur.xlsx
+++ b/feature/51-supprimer-les-exemples-de-longlet-ressources-par-cas-dusage/ig/StructureDefinition-FrPractitionerAgregateur.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-18T13:12:43+00:00</t>
+    <t>2024-07-18T13:45:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/feature/51-supprimer-les-exemples-de-longlet-ressources-par-cas-dusage/ig/StructureDefinition-FrPractitionerAgregateur.xlsx
+++ b/feature/51-supprimer-les-exemples-de-longlet-ressources-par-cas-dusage/ig/StructureDefinition-FrPractitionerAgregateur.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-18T13:45:25+00:00</t>
+    <t>2024-07-18T13:55:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
